--- a/hantei-sheets.xlsx
+++ b/hantei-sheets.xlsx
@@ -607,13 +607,6 @@
       <c r="C8" s="5"/>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -742,13 +735,6 @@
       <c r="C10" s="5"/>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -855,13 +841,6 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -988,13 +967,6 @@
       <c r="D11" s="5"/>
     </row>
     <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1163,13 +1135,6 @@
       <c r="D12" s="5"/>
     </row>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1415,13 +1380,6 @@
       <c r="G22" s="5"/>
     </row>
     <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1602,13 +1560,6 @@
       <c r="H14" s="5"/>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1734,13 +1685,6 @@
       <c r="B12" s="5"/>
     </row>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -1982,13 +1926,6 @@
       <c r="B19" s="5"/>
     </row>
     <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2115,13 +2052,6 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2248,13 +2178,6 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2370,13 +2293,6 @@
       <c r="C9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2503,13 +2419,6 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2606,13 +2515,6 @@
       <c r="D8" s="5"/>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2725,13 +2627,6 @@
       <c r="D8" s="5"/>
     </row>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2847,13 +2742,6 @@
       <c r="C9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2989,13 +2877,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3115,13 +2996,6 @@
       <c r="A11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">参考：総務省・経済産業省「AI事業者ガイドライン」第1.2版（2026年）、個人情報保護委員会「生成AIサービスの利用に関する注意喚起等」（2023年）、文化庁「AIと著作権に関する考え方について」（2024年）、日本ディープラーニング協会「生成AIの利用ガイドライン」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
         </is>
       </c>
     </row>
@@ -3265,13 +3139,6 @@
       <c r="H10" s="5"/>
     </row>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3477,13 +3344,6 @@
       <c r="B18" s="5"/>
     </row>
     <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3595,13 +3455,6 @@
       </c>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -3924,13 +3777,6 @@
       <c r="B27" s="5"/>
     </row>
     <row r="28"/>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4064,13 +3910,6 @@
       <c r="B14" s="5"/>
     </row>
     <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4220,13 +4059,6 @@
       <c r="B13" s="5"/>
     </row>
     <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4353,13 +4185,6 @@
       <c r="D9" s="5"/>
     </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4493,13 +4318,6 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">『SaaSか、外注か、AIで自作か ― IT担当者がいない会社のための26の判断』（paaz）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/hantei-sheets.xlsx
+++ b/hantei-sheets.xlsx
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">再試験（日付・結果）</t>
+          <t xml:space="preserve">再テスト（日付・結果）</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,20 @@
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">量（本番に近い件数・人数で試した／未）</t>
+        </is>
+      </c>
+      <c r="B19" s="5"/>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">資料（説明書・設計資料・ソースコード・保守連絡先）</t>
         </is>
       </c>
-      <c r="B19" s="5"/>
-    </row>
-    <row r="20"/>
+      <c r="B20" s="5"/>
+    </row>
+    <row r="21"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2995,7 +3003,7 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">参考：総務省・経済産業省「AI事業者ガイドライン」第1.2版（2026年）、個人情報保護委員会「生成AIサービスの利用に関する注意喚起等」（2023年）、文化庁「AIと著作権に関する考え方について」（2024年）、日本ディープラーニング協会「生成AIの利用ガイドライン」</t>
+          <t xml:space="preserve">参考：総務省・経済産業省「AI事業者ガイドライン」第1.2版（2026年）、個人情報保護委員会「生成AIサービスの利用に関する注意喚起等」（2023年）、文化審議会著作権分科会法制度小委員会「AIと著作権に関する考え方について」（2024年、文化庁が公表）、日本ディープラーニング協会「生成AIの利用ガイドライン」</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3366,7 @@
   <cols>
     <col min="1" max="1" width="39.6" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="42.3" customWidth="1"/>
+    <col min="3" max="3" width="41.4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3411,7 +3419,7 @@
       <c r="B6" s="5"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">アカウントの発行・停止、パソコンの初期設定 など</t>
+          <t xml:space="preserve">アカウントの発行・停止、パソコンの初期設定など</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3432,7 @@
       <c r="B7" s="5"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">保守会社、SaaSの提供会社 など</t>
+          <t xml:space="preserve">保守会社、SaaSの提供会社など</t>
         </is>
       </c>
     </row>
@@ -4001,12 +4009,12 @@
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5年の総額</t>
+          <t xml:space="preserve">浮いた時間の使い道</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">初期の費用 ＋ 毎年の費用 × 5</t>
+          <t xml:space="preserve">誰が、何に充てるか</t>
         </is>
       </c>
       <c r="C8" s="5"/>
@@ -4014,12 +4022,12 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">支払いの時期と資金</t>
+          <t xml:space="preserve">5年の総額</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">いつ、いくら払うか。立て替えられるか</t>
+          <t xml:space="preserve">初期の費用 ＋ 毎年の費用 × 5</t>
         </is>
       </c>
       <c r="C9" s="5"/>
@@ -4027,38 +4035,51 @@
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">支払いの時期と資金</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">いつ、いくら払うか。立て替えられるか</t>
+        </is>
+      </c>
+      <c r="C10" s="5"/>
+    </row>
+    <row r="11" ht="42" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">効果を測る物差し</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">使い始める前と後で比べる数字</t>
         </is>
       </c>
-      <c r="C10" s="5"/>
-    </row>
-    <row r="11"/>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="C11" s="5"/>
+    </row>
+    <row r="12"/>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">項目</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">記入欄</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="42" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">数えにくい効果</t>
         </is>
       </c>
-      <c r="B13" s="5"/>
-    </row>
-    <row r="14"/>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4136,7 +4157,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">総額（月額×人数×年数）、最低契約期間、値上げ、解約</t>
+          <t xml:space="preserve">総額（月額×人数×12か月×年数）、最低契約期間、値上げ、解約</t>
         </is>
       </c>
       <c r="C6" s="5"/>
@@ -4198,7 +4219,7 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="21.6" customWidth="1"/>
-    <col min="2" max="2" width="43.2" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
   </cols>
@@ -4276,7 +4297,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">個人情報やお金に関わるデータを扱うか</t>
+          <t xml:space="preserve">顧客の個人情報やお金に関わるデータなど、機密性の高いデータを扱うか</t>
         </is>
       </c>
       <c r="C7" s="5"/>
